--- a/data/google_news_dedup_audit_03_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_03_0426_UTC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,400 +445,253 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
-        <v>2</v>
-      </c>
       <c r="C2" t="n">
-        <v>0.7534030079841614</v>
+        <v>0.7660238742828369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Amazon to add 3.5% fuel surcharge for sellers as Iran war disrupts oil supply and raises logistics costs - Storyboard18</t>
+          <t>Royal Mail issues urgent update as households warned there are 'no deliveries' - The Mirror</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Amazon to apply 3.5% fuel and logistics surcharge on fulfillment - Supply Chain Dive</t>
+          <t>Royal Mail issues warning to Scottish households as there are 'no deliveries' - Glasgow Live</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" t="n">
         <v>3</v>
       </c>
-      <c r="B3" t="n">
-        <v>4</v>
-      </c>
       <c r="C3" t="n">
-        <v>0.7708263397216797</v>
+        <v>0.7897746562957764</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Royal Mail issues delivery disruption alert for 28 postcodes today — full list - The Mirror</t>
+          <t>Royal Mail issues urgent update as households warned there are 'no deliveries' - The Mirror</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Postcodes in Wales hit by Royal Mail delivery disruption today — full list - Wales Online</t>
+          <t>Royal Mail says there are 'no deliveries' as it issues urgent update - Daily Express</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8505051136016846</v>
+        <v>0.8084698915481567</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Royal Mail issues delivery disruption alert for 28 postcodes today — full list - The Mirror</t>
+          <t>Royal Mail issues urgent update as households warned there are 'no deliveries' - The Mirror</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Royal Mail issues delivery disruption alert for 4 Merseyside postcodes today — full list - Liverpool Echo</t>
+          <t>Royal Mail issues urgent warning as Merseyside households told there are 'no deliveries' - Liverpool Echo</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8503617644309998</v>
+        <v>0.6804419755935669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>What’s open on Good Friday 2026? Banks, mail, UPS and FedEx hours - democratandchronicle.com</t>
+          <t>Royal Mail issues urgent update as households warned there are 'no deliveries' - The Mirror</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Good Friday 2026 in US: What’s open and closed on April 3; Check banks, USPS, UPS, FedEx services status - The Times of India</t>
+          <t>Royal Mail warns Leicester postcodes there are 'no deliveries' in major update - Leicester Mercury</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7914486527442932</v>
+        <v>0.9624046087265015</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Arrestatie bij politieactie in Maastricht, persoon met zak over hoofd uit woning gehaald - De Limburger</t>
+          <t>Said Cherkaoui krijgt levenslang voor dodelijke steekpartij op Davy Veraghtert (39) in Berchem - HLN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Arrestatie bij politieactie in Maastricht - De Limburger</t>
+          <t>Said Cherkaoui krijgt levenslang voor dodelijke steekpartij op Davy Veraghtert (39) in Berchem - pzc.nl</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9787419438362122</v>
+        <v>0.7173600196838379</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ASSISEN. Said Cherkaoui is schuldig bevonden aan moord op Davy Veraghtert - GVA</t>
+          <t>Soldiers join police to patrol Brussels’ public transport - belganewsagency.eu</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ASSISEN. Said Cherkaoui is schuldig bevonden aan moord op Davy Veraghtert - Nieuwsblad</t>
+          <t>Soldiers on patrol in Brussels’ metro and railway stations - VRT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B8" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9556260108947754</v>
+        <v>0.8484503030776978</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Drugsoorlog in Brussel blijft duren: teller dit jaar al op 22 schietpartijen na nieuw incident in Anderlecht | Foto - HLN</t>
+          <t>Teenage boy shot dead and three arrested for murder in Woolwich - bbc.co.uk</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Drugsoorlog in Brussel blijft duren: teller dit jaar al op 22 schietpartijen na nieuw incident in Anderlecht - HLN</t>
+          <t>Woolwich shooting: Boy, 14, shot dead in south London - The Telegraph</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8218574523925781</v>
+        <v>0.788488507270813</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Goldman Paris is warned of Iran group bomb threat: Parisien - The Straits Times</t>
+          <t>Teenage boy shot dead and three arrested for murder in Woolwich - bbc.co.uk</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Goldman Paris under police watch after bomb threat linked to Iran group - ایران اینترنشنال</t>
+          <t>Boy, 14, shot dead in London - as three teenagers arrested on suspicion of murder - Sky News</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B10" t="n">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7507656812667847</v>
+        <v>0.7060708999633789</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Goldman Paris is warned of Iran group bomb threat: Parisien - The Straits Times</t>
+          <t>Teenage boy shot dead and three arrested for murder in Woolwich - bbc.co.uk</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Goldman Sachs (GS.US) Paris HQ Receives Bomb Threat; France Tightens Security at US Banks - aastocks.com</t>
+          <t>London shooting: Teenage boy killed, 3 arrested - News.az</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="B11" t="n">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7877653241157532</v>
+        <v>0.7284245491027832</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Arrests after man shot dead in Woolwich - BBC</t>
+          <t>Teenage boy shot dead and three arrested for murder in Woolwich - bbc.co.uk</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LIVE updates as crime scene in place after man killed in Woolwich shooting - London Now</t>
+          <t>Three arrested after boy, 14, shot dead in London - The Independent</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="B12" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7784018516540527</v>
+        <v>0.7003551721572876</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Arrests after man shot dead in Woolwich - BBC</t>
+          <t>Teenage boy shot dead and three arrested for murder in Woolwich - bbc.co.uk</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Three men arrested after man shot dead outside block of flats in Woolwich - London Now</t>
+          <t>LIVE updates as investigation continues after boy shot dead in Woolwich - London Now</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="B13" t="n">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8269913196563721</v>
+        <v>0.7743963003158569</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Arrests after man shot dead in Woolwich - BBC</t>
+          <t>Teenage boy shot dead and three arrested for murder in Woolwich - bbc.co.uk</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Crime scene in place after man killed in Woolwich shooting - London Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>64</v>
-      </c>
-      <c r="B14" t="n">
-        <v>70</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.9325194954872131</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Murder probe as man dies in second fatal London shooting in a week - London Evening Standard</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Murder probe as man dies in second fatal London shooting in a week - MSN</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>65</v>
-      </c>
-      <c r="B15" t="n">
-        <v>80</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.7073154449462891</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Man killed in shooting and woman stabbed to death in horror 24 hours across London - London Now</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Woman stabbed to death after letting man into her home in Croydon - London Now</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>68</v>
-      </c>
-      <c r="B16" t="n">
-        <v>71</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.7106589674949646</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Windsor man charged with murder in New London shooting of 42-year-old on Connecticut Avenue - CT Insider</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Man charged with murder after February shooting in New London - WTNH.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>68</v>
-      </c>
-      <c r="B17" t="n">
-        <v>83</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.5915751457214355</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Windsor man charged with murder in New London shooting of 42-year-old on Connecticut Avenue - CT Insider</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Man arrested for murder after February New London shooting - fox61.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>74</v>
-      </c>
-      <c r="B18" t="n">
-        <v>82</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.7206319570541382</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Elementary school evacuated over 'written bomb threat': Board officials - London Free Press</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Ingersoll school evacuated after written bomb threat found on property - CBC</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>74</v>
-      </c>
-      <c r="B19" t="n">
-        <v>85</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.7949435710906982</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Elementary school evacuated over 'written bomb threat': Board officials - London Free Press</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Written bomb threat prompts evacuation of elementary school in Ingersoll - CTV News</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>91</v>
-      </c>
-      <c r="B20" t="n">
-        <v>104</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.7064453363418579</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Omicidio Custra, nuovo round. La pena di Ventura non è estinta: "Attualità dell’interesse punitivo" - Il Giorno</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Delitto Custra, la Cassazione riapre il caso: “Ridiscutere la prescrizione per Ventura” - Il Giorno</t>
+          <t>Woolwich fatal shooting victim confirmed to be 14-year-old boy - thisislocallondon.co.uk</t>
         </is>
       </c>
     </row>
